--- a/practice/answers/q058.xlsx
+++ b/practice/answers/q058.xlsx
@@ -70115,14 +70115,14 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>(b) 2020 has the most AAC Brandon results (94); the count then slips every year to 81 by 2025.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>(c) A defensible reading: the more profit-oriented growers were the likeliest to move on to newer varieties, leaving Brandon with growers who push yields less. If so, Brandon's average yield in later years reflects who still grows it as much as the variety itself -- the falling count is a warning about changing composition, not just popularity.</t>

--- a/practice/answers/q058.xlsx
+++ b/practice/answers/q058.xlsx
@@ -70118,7 +70118,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>(b) 2020 has the most AAC Brandon results (94); the count then slips every year to 81 by 2025.</t>
+          <t>(b) 2020 has the most AAC Brandon results (94); the count then drifts down to 81 by 2025.</t>
         </is>
       </c>
     </row>
